--- a/news_daily/2026-08-11.xlsx
+++ b/news_daily/2026-08-11.xlsx
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f1eb9f6042984ad39f51ae230fcb4e0e</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>58a51e006942323eade1213a</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1027,10 +1039,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1846,28 +1870,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1911,7 +1939,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1920,7 +1948,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>e89493f502ae4aa0b5fd48f484890a9f</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>65b2a85124b795f692dd36d5</t>
@@ -1941,7 +1973,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1985,10 +2021,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2024,28 +2072,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2089,7 +2141,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2098,7 +2150,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>efc12f566ce047fab53a81967a956e1b</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>b0a1e3b23d05798ab63a821c</t>
@@ -2119,7 +2175,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2163,10 +2223,22 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2784,28 +2856,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2849,7 +2925,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2858,7 +2934,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>c47a16124887472690cffd31898cc1b4</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>d310fa2a17acd283a61145bf</t>
@@ -2879,7 +2959,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2915,10 +2999,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3540,28 +3636,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3605,7 +3705,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3614,7 +3714,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>6d295a1377fc4c8f9288cc51eff3687c</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>277a1d68613b34719a059406</t>
@@ -3635,7 +3739,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3679,10 +3787,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4106,28 +4226,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4171,7 +4295,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4180,7 +4304,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>c0c81697b620407bb30ac7f9d457377e</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>7d11c80581f0cc600af1b777</t>
@@ -4201,7 +4329,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4245,10 +4377,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5060,28 +5204,32 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5125,7 +5273,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -5134,7 +5282,11 @@
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>519f7032ee4341728bbc42d6f2199750</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>582598527e988ac3d29e1cdb</t>
@@ -5155,7 +5307,11 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="2" t="inlineStr"/>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
@@ -5199,10 +5355,22 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
-      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ24" s="2" t="inlineStr"/>
-      <c r="BK24" s="2" t="inlineStr"/>
-      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5626,28 +5794,32 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5691,7 +5863,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -5700,7 +5872,11 @@
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>d3439861506d41b5befcb634e481c84a</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>cbfe51d46ea73c0befcdfe3e</t>
@@ -5721,7 +5897,11 @@
       <c r="AL27" s="2" t="inlineStr"/>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr"/>
-      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="2" t="inlineStr"/>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
@@ -5765,10 +5945,22 @@
         </is>
       </c>
       <c r="BH27" s="2" t="inlineStr"/>
-      <c r="BI27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ27" s="2" t="inlineStr"/>
-      <c r="BK27" s="2" t="inlineStr"/>
-      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5804,28 +5996,32 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5869,7 +6065,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -5878,7 +6074,11 @@
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0f16c5587a9b42569320bbd80e53c5d6</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>c0bdd7f562e1850f58c2146e</t>
@@ -5899,7 +6099,11 @@
       <c r="AL28" s="2" t="inlineStr"/>
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr"/>
-      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="2" t="inlineStr"/>
       <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
@@ -5943,10 +6147,22 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
-      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="2" t="inlineStr"/>
-      <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5982,28 +6198,32 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6047,7 +6267,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -6056,7 +6276,11 @@
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>f22d41c940e94f65acff6d903c961199</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>5e78c96e0d1bfa2180f71876</t>
@@ -6077,7 +6301,11 @@
       <c r="AL29" s="2" t="inlineStr"/>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr"/>
-      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="2" t="inlineStr"/>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -6121,10 +6349,22 @@
         </is>
       </c>
       <c r="BH29" s="2" t="inlineStr"/>
-      <c r="BI29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ29" s="2" t="inlineStr"/>
-      <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,28 +6400,32 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6225,7 +6469,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -6234,7 +6478,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>36bfcb80d9e24f5994eb88c50239686d</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>85d0e5abf1ab3bb2a92f94a7</t>
@@ -6255,7 +6503,11 @@
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="2" t="inlineStr"/>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="inlineStr"/>
@@ -6299,10 +6551,22 @@
         </is>
       </c>
       <c r="BH30" s="2" t="inlineStr"/>
-      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -6536,28 +6800,32 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6601,7 +6869,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -6610,7 +6878,11 @@
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
-      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>a3f29e5c53864dc28576aa2e8e6f896e</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>ee4d4c9270df6fb081c40253</t>
@@ -6631,7 +6903,11 @@
       <c r="AL32" s="2" t="inlineStr"/>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
-      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
@@ -6667,10 +6943,22 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
-      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ32" s="2" t="inlineStr"/>
-      <c r="BK32" s="2" t="inlineStr"/>
-      <c r="BL32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6706,28 +6994,32 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6771,7 +7063,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -6780,7 +7072,11 @@
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr"/>
-      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>29ebe4bfbd0b4473b5a642bc69dc88ff</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>04c403d100533a4db495fa55</t>
@@ -6801,7 +7097,11 @@
       <c r="AL33" s="2" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
-      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="2" t="inlineStr"/>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -6845,10 +7145,22 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
-      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ33" s="2" t="inlineStr"/>
-      <c r="BK33" s="2" t="inlineStr"/>
-      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6884,28 +7196,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6949,7 +7265,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -6958,7 +7274,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>724e6efac4f2471082c965a6a2a092dc</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>ba6972de3ec476e718621703</t>
@@ -6979,7 +7299,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -7015,10 +7339,22 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7636,28 +7972,32 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -7701,7 +8041,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -7710,7 +8050,11 @@
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr"/>
-      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>5363dff3441d452d95fd332772e1cae6</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>aa018ee37b79755fd11cbb75</t>
@@ -7731,7 +8075,11 @@
       <c r="AL38" s="2" t="inlineStr"/>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
-      <c r="AO38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="2" t="inlineStr"/>
       <c r="AQ38" s="2" t="inlineStr"/>
       <c r="AR38" s="2" t="inlineStr"/>
@@ -7775,10 +8123,22 @@
         </is>
       </c>
       <c r="BH38" s="2" t="inlineStr"/>
-      <c r="BI38" s="2" t="inlineStr"/>
+      <c r="BI38" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ38" s="2" t="inlineStr"/>
-      <c r="BK38" s="2" t="inlineStr"/>
-      <c r="BL38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7814,28 +8174,32 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7879,7 +8243,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -7888,7 +8252,11 @@
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr"/>
-      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>6155afe1d8d24f42998cf0fc9a2a38bc</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>3c6b490da53f88f0386d1083</t>
@@ -7909,7 +8277,11 @@
       <c r="AL39" s="2" t="inlineStr"/>
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr"/>
-      <c r="AO39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP39" s="2" t="inlineStr"/>
       <c r="AQ39" s="2" t="inlineStr"/>
       <c r="AR39" s="2" t="inlineStr"/>
@@ -7953,10 +8325,22 @@
         </is>
       </c>
       <c r="BH39" s="2" t="inlineStr"/>
-      <c r="BI39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ39" s="2" t="inlineStr"/>
-      <c r="BK39" s="2" t="inlineStr"/>
-      <c r="BL39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7992,28 +8376,32 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -8057,7 +8445,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -8066,7 +8454,11 @@
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr"/>
-      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>9a15b67d726b4751b95901af8d6c6804</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>6c9f455a149494b70a102465</t>
@@ -8087,7 +8479,11 @@
       <c r="AL40" s="2" t="inlineStr"/>
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr"/>
-      <c r="AO40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP40" s="2" t="inlineStr"/>
       <c r="AQ40" s="2" t="inlineStr"/>
       <c r="AR40" s="2" t="inlineStr"/>
@@ -8131,10 +8527,22 @@
         </is>
       </c>
       <c r="BH40" s="2" t="inlineStr"/>
-      <c r="BI40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ40" s="2" t="inlineStr"/>
-      <c r="BK40" s="2" t="inlineStr"/>
-      <c r="BL40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8170,28 +8578,32 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -8235,7 +8647,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -8244,7 +8656,11 @@
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr"/>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>9a2caa82da754c16806e65e9363fc2da</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>6f32166fda81f68029be595c</t>
@@ -8265,7 +8681,11 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
-      <c r="AO41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="2" t="inlineStr"/>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
@@ -8309,10 +8729,22 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
-      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8740,28 +9172,32 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -8805,7 +9241,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -8814,7 +9250,11 @@
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr"/>
-      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>ce690c25d9e643279dce38b6c7956e66</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
           <t>bfa61ba710e547ae62d67d83</t>
@@ -8835,7 +9275,11 @@
       <c r="AL44" s="2" t="inlineStr"/>
       <c r="AM44" s="2" t="inlineStr"/>
       <c r="AN44" s="2" t="inlineStr"/>
-      <c r="AO44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP44" s="2" t="inlineStr"/>
       <c r="AQ44" s="2" t="inlineStr"/>
       <c r="AR44" s="2" t="inlineStr"/>
@@ -8879,10 +9323,22 @@
         </is>
       </c>
       <c r="BH44" s="2" t="inlineStr"/>
-      <c r="BI44" s="2" t="inlineStr"/>
+      <c r="BI44" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ44" s="2" t="inlineStr"/>
-      <c r="BK44" s="2" t="inlineStr"/>
-      <c r="BL44" s="2" t="inlineStr"/>
+      <c r="BK44" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8918,28 +9374,32 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -8983,7 +9443,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -8992,7 +9452,11 @@
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr"/>
-      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>5bbb871d9f3e478bb26d8ae8c8c7461a</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>f15061687832b2a92f4de3c7</t>
@@ -9013,7 +9477,11 @@
       <c r="AL45" s="2" t="inlineStr"/>
       <c r="AM45" s="2" t="inlineStr"/>
       <c r="AN45" s="2" t="inlineStr"/>
-      <c r="AO45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP45" s="2" t="inlineStr"/>
       <c r="AQ45" s="2" t="inlineStr"/>
       <c r="AR45" s="2" t="inlineStr"/>
@@ -9057,10 +9525,22 @@
         </is>
       </c>
       <c r="BH45" s="2" t="inlineStr"/>
-      <c r="BI45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ45" s="2" t="inlineStr"/>
-      <c r="BK45" s="2" t="inlineStr"/>
-      <c r="BL45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9111,13 +9591,17 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -9170,7 +9654,11 @@
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr"/>
-      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>7ecdbde1d0404f6ea8a62f71aa654cb8</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>f36d7b0528d751adf668dd55</t>
@@ -9191,7 +9679,11 @@
       <c r="AL46" s="2" t="inlineStr"/>
       <c r="AM46" s="2" t="inlineStr"/>
       <c r="AN46" s="2" t="inlineStr"/>
-      <c r="AO46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP46" s="2" t="inlineStr"/>
       <c r="AQ46" s="2" t="inlineStr"/>
       <c r="AR46" s="2" t="inlineStr"/>
@@ -9229,8 +9721,16 @@
       <c r="BH46" s="2" t="inlineStr"/>
       <c r="BI46" s="2" t="inlineStr"/>
       <c r="BJ46" s="2" t="inlineStr"/>
-      <c r="BK46" s="2" t="inlineStr"/>
-      <c r="BL46" s="2" t="inlineStr"/>
+      <c r="BK46" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9452,28 +9952,32 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -9517,7 +10021,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -9526,7 +10030,11 @@
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr"/>
-      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>14169472054349fa902f92c0f96b61c7</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>7b0229f291caa199fba878fc</t>
@@ -9547,7 +10055,11 @@
       <c r="AL48" s="2" t="inlineStr"/>
       <c r="AM48" s="2" t="inlineStr"/>
       <c r="AN48" s="2" t="inlineStr"/>
-      <c r="AO48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP48" s="2" t="inlineStr"/>
       <c r="AQ48" s="2" t="inlineStr"/>
       <c r="AR48" s="2" t="inlineStr"/>
@@ -9591,10 +10103,22 @@
         </is>
       </c>
       <c r="BH48" s="2" t="inlineStr"/>
-      <c r="BI48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ48" s="2" t="inlineStr"/>
-      <c r="BK48" s="2" t="inlineStr"/>
-      <c r="BL48" s="2" t="inlineStr"/>
+      <c r="BK48" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -10212,28 +10736,32 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -10277,7 +10805,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -10286,7 +10814,11 @@
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr"/>
-      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>85424cd66c87488e9074268bd6195b48</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>81ba67fbead2ebdd4405cabb</t>
@@ -10307,7 +10839,11 @@
       <c r="AL52" s="2" t="inlineStr"/>
       <c r="AM52" s="2" t="inlineStr"/>
       <c r="AN52" s="2" t="inlineStr"/>
-      <c r="AO52" s="2" t="inlineStr"/>
+      <c r="AO52" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP52" s="2" t="inlineStr"/>
       <c r="AQ52" s="2" t="inlineStr"/>
       <c r="AR52" s="2" t="inlineStr"/>
@@ -10351,10 +10887,22 @@
         </is>
       </c>
       <c r="BH52" s="2" t="inlineStr"/>
-      <c r="BI52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ52" s="2" t="inlineStr"/>
-      <c r="BK52" s="2" t="inlineStr"/>
-      <c r="BL52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -10580,28 +11128,32 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -10645,7 +11197,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -10654,7 +11206,11 @@
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>d7c7dd65e07c485ca52e28cafe60a4b1</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>ca81b52fb9b4f2d7734e5e04</t>
@@ -10675,7 +11231,11 @@
       <c r="AL54" s="2" t="inlineStr"/>
       <c r="AM54" s="2" t="inlineStr"/>
       <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP54" s="2" t="inlineStr"/>
       <c r="AQ54" s="2" t="inlineStr"/>
       <c r="AR54" s="2" t="inlineStr"/>
@@ -10719,10 +11279,22 @@
         </is>
       </c>
       <c r="BH54" s="2" t="inlineStr"/>
-      <c r="BI54" s="2" t="inlineStr"/>
+      <c r="BI54" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ54" s="2" t="inlineStr"/>
-      <c r="BK54" s="2" t="inlineStr"/>
-      <c r="BL54" s="2" t="inlineStr"/>
+      <c r="BK54" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10758,28 +11330,32 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -10823,7 +11399,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -10832,7 +11408,11 @@
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr"/>
-      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>48a408773b594e63bed2900736ecbc8a</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
           <t>b9ebd01b73783f8a3942d499</t>
@@ -10853,7 +11433,11 @@
       <c r="AL55" s="2" t="inlineStr"/>
       <c r="AM55" s="2" t="inlineStr"/>
       <c r="AN55" s="2" t="inlineStr"/>
-      <c r="AO55" s="2" t="inlineStr"/>
+      <c r="AO55" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="2" t="inlineStr"/>
       <c r="AQ55" s="2" t="inlineStr"/>
       <c r="AR55" s="2" t="inlineStr"/>
@@ -10897,10 +11481,22 @@
         </is>
       </c>
       <c r="BH55" s="2" t="inlineStr"/>
-      <c r="BI55" s="2" t="inlineStr"/>
+      <c r="BI55" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ55" s="2" t="inlineStr"/>
-      <c r="BK55" s="2" t="inlineStr"/>
-      <c r="BL55" s="2" t="inlineStr"/>
+      <c r="BK55" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10951,13 +11547,17 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -11010,7 +11610,11 @@
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr"/>
-      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>66c0a2fcd23542b3bcdba3c1145c9ade</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
           <t>58665faa10c87e6474307138</t>
@@ -11031,7 +11635,11 @@
       <c r="AL56" s="2" t="inlineStr"/>
       <c r="AM56" s="2" t="inlineStr"/>
       <c r="AN56" s="2" t="inlineStr"/>
-      <c r="AO56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP56" s="2" t="inlineStr"/>
       <c r="AQ56" s="2" t="inlineStr"/>
       <c r="AR56" s="2" t="inlineStr"/>
@@ -11077,8 +11685,16 @@
       <c r="BH56" s="2" t="inlineStr"/>
       <c r="BI56" s="2" t="inlineStr"/>
       <c r="BJ56" s="2" t="inlineStr"/>
-      <c r="BK56" s="2" t="inlineStr"/>
-      <c r="BL56" s="2" t="inlineStr"/>
+      <c r="BK56" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -11114,28 +11730,32 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -11179,7 +11799,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -11188,7 +11808,11 @@
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr"/>
-      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>3cf1fc7db6594468b03a2200f4ee5d83</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
           <t>febc96252d48073e11661326</t>
@@ -11209,7 +11833,11 @@
       <c r="AL57" s="2" t="inlineStr"/>
       <c r="AM57" s="2" t="inlineStr"/>
       <c r="AN57" s="2" t="inlineStr"/>
-      <c r="AO57" s="2" t="inlineStr"/>
+      <c r="AO57" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP57" s="2" t="inlineStr"/>
       <c r="AQ57" s="2" t="inlineStr"/>
       <c r="AR57" s="2" t="inlineStr"/>
@@ -11253,10 +11881,22 @@
         </is>
       </c>
       <c r="BH57" s="2" t="inlineStr"/>
-      <c r="BI57" s="2" t="inlineStr"/>
+      <c r="BI57" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ57" s="2" t="inlineStr"/>
-      <c r="BK57" s="2" t="inlineStr"/>
-      <c r="BL57" s="2" t="inlineStr"/>
+      <c r="BK57" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -12472,28 +13112,32 @@
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -12537,7 +13181,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -12546,7 +13190,11 @@
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr"/>
-      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>9e48e67dcfc5417f89914d1a8e2fcd64</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>c1b2e971406bde7e9114c378</t>
@@ -12567,7 +13215,11 @@
       <c r="AL64" s="2" t="inlineStr"/>
       <c r="AM64" s="2" t="inlineStr"/>
       <c r="AN64" s="2" t="inlineStr"/>
-      <c r="AO64" s="2" t="inlineStr"/>
+      <c r="AO64" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP64" s="2" t="inlineStr"/>
       <c r="AQ64" s="2" t="inlineStr"/>
       <c r="AR64" s="2" t="inlineStr"/>
@@ -12611,10 +13263,22 @@
         </is>
       </c>
       <c r="BH64" s="2" t="inlineStr"/>
-      <c r="BI64" s="2" t="inlineStr"/>
+      <c r="BI64" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ64" s="2" t="inlineStr"/>
-      <c r="BK64" s="2" t="inlineStr"/>
-      <c r="BL64" s="2" t="inlineStr"/>
+      <c r="BK64" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -13236,28 +13900,32 @@
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -13301,7 +13969,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -13310,7 +13978,11 @@
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr"/>
-      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>cee16bd997004a4b8c665552b3405fbc</t>
+        </is>
+      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>183a6bec08104f28c19d7330</t>
@@ -13331,7 +14003,11 @@
       <c r="AL68" s="2" t="inlineStr"/>
       <c r="AM68" s="2" t="inlineStr"/>
       <c r="AN68" s="2" t="inlineStr"/>
-      <c r="AO68" s="2" t="inlineStr"/>
+      <c r="AO68" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP68" s="2" t="inlineStr"/>
       <c r="AQ68" s="2" t="inlineStr"/>
       <c r="AR68" s="2" t="inlineStr"/>
@@ -13367,10 +14043,22 @@
         </is>
       </c>
       <c r="BH68" s="2" t="inlineStr"/>
-      <c r="BI68" s="2" t="inlineStr"/>
+      <c r="BI68" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ68" s="2" t="inlineStr"/>
-      <c r="BK68" s="2" t="inlineStr"/>
-      <c r="BL68" s="2" t="inlineStr"/>
+      <c r="BK68" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13406,28 +14094,32 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -13471,7 +14163,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -13480,7 +14172,11 @@
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr"/>
-      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>b3899006430049548c90eec874c3c7ea</t>
+        </is>
+      </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>a4d52739d5de611d45184870</t>
@@ -13501,7 +14197,11 @@
       <c r="AL69" s="2" t="inlineStr"/>
       <c r="AM69" s="2" t="inlineStr"/>
       <c r="AN69" s="2" t="inlineStr"/>
-      <c r="AO69" s="2" t="inlineStr"/>
+      <c r="AO69" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP69" s="2" t="inlineStr"/>
       <c r="AQ69" s="2" t="inlineStr"/>
       <c r="AR69" s="2" t="inlineStr"/>
@@ -13545,10 +14245,22 @@
         </is>
       </c>
       <c r="BH69" s="2" t="inlineStr"/>
-      <c r="BI69" s="2" t="inlineStr"/>
+      <c r="BI69" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ69" s="2" t="inlineStr"/>
-      <c r="BK69" s="2" t="inlineStr"/>
-      <c r="BL69" s="2" t="inlineStr"/>
+      <c r="BK69" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13584,28 +14296,32 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -13649,7 +14365,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -13658,7 +14374,11 @@
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr"/>
-      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>78264d4921d84fcebdee29356a9e494b</t>
+        </is>
+      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
           <t>d9d2b39259006de76768d596</t>
@@ -13679,7 +14399,11 @@
       <c r="AL70" s="2" t="inlineStr"/>
       <c r="AM70" s="2" t="inlineStr"/>
       <c r="AN70" s="2" t="inlineStr"/>
-      <c r="AO70" s="2" t="inlineStr"/>
+      <c r="AO70" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP70" s="2" t="inlineStr"/>
       <c r="AQ70" s="2" t="inlineStr"/>
       <c r="AR70" s="2" t="inlineStr"/>
@@ -13723,10 +14447,22 @@
         </is>
       </c>
       <c r="BH70" s="2" t="inlineStr"/>
-      <c r="BI70" s="2" t="inlineStr"/>
+      <c r="BI70" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ70" s="2" t="inlineStr"/>
-      <c r="BK70" s="2" t="inlineStr"/>
-      <c r="BL70" s="2" t="inlineStr"/>
+      <c r="BK70" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13762,28 +14498,32 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -13827,7 +14567,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -13836,7 +14576,11 @@
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr"/>
-      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>b9d15d35d4124977afba11c143fa02c3</t>
+        </is>
+      </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
           <t>3b37eb5825320d53b5863d8c</t>
@@ -13857,7 +14601,11 @@
       <c r="AL71" s="2" t="inlineStr"/>
       <c r="AM71" s="2" t="inlineStr"/>
       <c r="AN71" s="2" t="inlineStr"/>
-      <c r="AO71" s="2" t="inlineStr"/>
+      <c r="AO71" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP71" s="2" t="inlineStr"/>
       <c r="AQ71" s="2" t="inlineStr"/>
       <c r="AR71" s="2" t="inlineStr"/>
@@ -13901,10 +14649,22 @@
         </is>
       </c>
       <c r="BH71" s="2" t="inlineStr"/>
-      <c r="BI71" s="2" t="inlineStr"/>
+      <c r="BI71" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ71" s="2" t="inlineStr"/>
-      <c r="BK71" s="2" t="inlineStr"/>
-      <c r="BL71" s="2" t="inlineStr"/>
+      <c r="BK71" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -14324,28 +15084,32 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -14389,7 +15153,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -14398,7 +15162,11 @@
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr"/>
-      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>30a12452099548399c63b391477d24a1</t>
+        </is>
+      </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
           <t>ce489178f3c10266702b6f55</t>
@@ -14419,7 +15187,11 @@
       <c r="AL74" s="2" t="inlineStr"/>
       <c r="AM74" s="2" t="inlineStr"/>
       <c r="AN74" s="2" t="inlineStr"/>
-      <c r="AO74" s="2" t="inlineStr"/>
+      <c r="AO74" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP74" s="2" t="inlineStr"/>
       <c r="AQ74" s="2" t="inlineStr"/>
       <c r="AR74" s="2" t="inlineStr"/>
@@ -14463,10 +15235,22 @@
         </is>
       </c>
       <c r="BH74" s="2" t="inlineStr"/>
-      <c r="BI74" s="2" t="inlineStr"/>
+      <c r="BI74" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ74" s="2" t="inlineStr"/>
-      <c r="BK74" s="2" t="inlineStr"/>
-      <c r="BL74" s="2" t="inlineStr"/>
+      <c r="BK74" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -15084,28 +15868,32 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -15149,7 +15937,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -15158,7 +15946,11 @@
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr"/>
-      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>86e7985e12bf431e8fbb6509a29253b8</t>
+        </is>
+      </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
           <t>c66755324346c8830a433fdf</t>
@@ -15179,7 +15971,11 @@
       <c r="AL78" s="2" t="inlineStr"/>
       <c r="AM78" s="2" t="inlineStr"/>
       <c r="AN78" s="2" t="inlineStr"/>
-      <c r="AO78" s="2" t="inlineStr"/>
+      <c r="AO78" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP78" s="2" t="inlineStr"/>
       <c r="AQ78" s="2" t="inlineStr"/>
       <c r="AR78" s="2" t="inlineStr"/>
@@ -15223,10 +16019,22 @@
         </is>
       </c>
       <c r="BH78" s="2" t="inlineStr"/>
-      <c r="BI78" s="2" t="inlineStr"/>
+      <c r="BI78" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ78" s="2" t="inlineStr"/>
-      <c r="BK78" s="2" t="inlineStr"/>
-      <c r="BL78" s="2" t="inlineStr"/>
+      <c r="BK78" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -15456,28 +16264,32 @@
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -15521,7 +16333,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -15530,7 +16342,11 @@
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr"/>
-      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>79f094c87f0e4666aa9950ecaed66f84</t>
+        </is>
+      </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
           <t>3c12fc05bcc064bbdd70c806</t>
@@ -15551,7 +16367,11 @@
       <c r="AL80" s="2" t="inlineStr"/>
       <c r="AM80" s="2" t="inlineStr"/>
       <c r="AN80" s="2" t="inlineStr"/>
-      <c r="AO80" s="2" t="inlineStr"/>
+      <c r="AO80" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP80" s="2" t="inlineStr"/>
       <c r="AQ80" s="2" t="inlineStr"/>
       <c r="AR80" s="2" t="inlineStr"/>
@@ -15587,10 +16407,22 @@
         </is>
       </c>
       <c r="BH80" s="2" t="inlineStr"/>
-      <c r="BI80" s="2" t="inlineStr"/>
+      <c r="BI80" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ80" s="2" t="inlineStr"/>
-      <c r="BK80" s="2" t="inlineStr"/>
-      <c r="BL80" s="2" t="inlineStr"/>
+      <c r="BK80" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -16216,28 +17048,32 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -16281,7 +17117,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -16290,7 +17126,11 @@
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr"/>
-      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>3175c625f04a41328f8e7a1f4c5791cf</t>
+        </is>
+      </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
           <t>40d93f8795918bd8902f67d2</t>
@@ -16311,7 +17151,11 @@
       <c r="AL84" s="2" t="inlineStr"/>
       <c r="AM84" s="2" t="inlineStr"/>
       <c r="AN84" s="2" t="inlineStr"/>
-      <c r="AO84" s="2" t="inlineStr"/>
+      <c r="AO84" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP84" s="2" t="inlineStr"/>
       <c r="AQ84" s="2" t="inlineStr"/>
       <c r="AR84" s="2" t="inlineStr"/>
@@ -16355,10 +17199,22 @@
         </is>
       </c>
       <c r="BH84" s="2" t="inlineStr"/>
-      <c r="BI84" s="2" t="inlineStr"/>
+      <c r="BI84" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ84" s="2" t="inlineStr"/>
-      <c r="BK84" s="2" t="inlineStr"/>
-      <c r="BL84" s="2" t="inlineStr"/>
+      <c r="BK84" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -16394,28 +17250,32 @@
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -16459,7 +17319,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -16468,7 +17328,11 @@
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr"/>
-      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>5653d3bb4a47417bafd6b42f3f6eef02</t>
+        </is>
+      </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
           <t>7183e9104bfd2b9b8f60402d</t>
@@ -16489,7 +17353,11 @@
       <c r="AL85" s="2" t="inlineStr"/>
       <c r="AM85" s="2" t="inlineStr"/>
       <c r="AN85" s="2" t="inlineStr"/>
-      <c r="AO85" s="2" t="inlineStr"/>
+      <c r="AO85" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP85" s="2" t="inlineStr"/>
       <c r="AQ85" s="2" t="inlineStr"/>
       <c r="AR85" s="2" t="inlineStr"/>
@@ -16525,10 +17393,22 @@
         </is>
       </c>
       <c r="BH85" s="2" t="inlineStr"/>
-      <c r="BI85" s="2" t="inlineStr"/>
+      <c r="BI85" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ85" s="2" t="inlineStr"/>
-      <c r="BK85" s="2" t="inlineStr"/>
-      <c r="BL85" s="2" t="inlineStr"/>
+      <c r="BK85" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -16758,28 +17638,32 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -16823,7 +17707,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -16832,7 +17716,11 @@
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr"/>
-      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>7e63ce7eebf845d78967aab19b6b52f4</t>
+        </is>
+      </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
           <t>d3cffd669329d2b1073dd135</t>
@@ -16853,7 +17741,11 @@
       <c r="AL87" s="2" t="inlineStr"/>
       <c r="AM87" s="2" t="inlineStr"/>
       <c r="AN87" s="2" t="inlineStr"/>
-      <c r="AO87" s="2" t="inlineStr"/>
+      <c r="AO87" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP87" s="2" t="inlineStr"/>
       <c r="AQ87" s="2" t="inlineStr"/>
       <c r="AR87" s="2" t="inlineStr"/>
@@ -16897,10 +17789,22 @@
         </is>
       </c>
       <c r="BH87" s="2" t="inlineStr"/>
-      <c r="BI87" s="2" t="inlineStr"/>
+      <c r="BI87" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ87" s="2" t="inlineStr"/>
-      <c r="BK87" s="2" t="inlineStr"/>
-      <c r="BL87" s="2" t="inlineStr"/>
+      <c r="BK87" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -16951,13 +17855,17 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -17010,7 +17918,11 @@
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr"/>
-      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>ecfa1fd468394a39a5289aabd7687c30</t>
+        </is>
+      </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
           <t>547e2b390519a7b5f6cdeb0e</t>
@@ -17031,7 +17943,11 @@
       <c r="AL88" s="2" t="inlineStr"/>
       <c r="AM88" s="2" t="inlineStr"/>
       <c r="AN88" s="2" t="inlineStr"/>
-      <c r="AO88" s="2" t="inlineStr"/>
+      <c r="AO88" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP88" s="2" t="inlineStr"/>
       <c r="AQ88" s="2" t="inlineStr"/>
       <c r="AR88" s="2" t="inlineStr"/>
@@ -17077,8 +17993,16 @@
       <c r="BH88" s="2" t="inlineStr"/>
       <c r="BI88" s="2" t="inlineStr"/>
       <c r="BJ88" s="2" t="inlineStr"/>
-      <c r="BK88" s="2" t="inlineStr"/>
-      <c r="BL88" s="2" t="inlineStr"/>
+      <c r="BK88" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -17114,28 +18038,32 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -17179,7 +18107,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -17188,7 +18116,11 @@
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr"/>
-      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>15743acc1bcc48c896ed752dc8ae05f9</t>
+        </is>
+      </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
           <t>48e84e94dc87271159329c75</t>
@@ -17209,7 +18141,11 @@
       <c r="AL89" s="2" t="inlineStr"/>
       <c r="AM89" s="2" t="inlineStr"/>
       <c r="AN89" s="2" t="inlineStr"/>
-      <c r="AO89" s="2" t="inlineStr"/>
+      <c r="AO89" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP89" s="2" t="inlineStr"/>
       <c r="AQ89" s="2" t="inlineStr"/>
       <c r="AR89" s="2" t="inlineStr"/>
@@ -17253,10 +18189,22 @@
         </is>
       </c>
       <c r="BH89" s="2" t="inlineStr"/>
-      <c r="BI89" s="2" t="inlineStr"/>
+      <c r="BI89" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ89" s="2" t="inlineStr"/>
-      <c r="BK89" s="2" t="inlineStr"/>
-      <c r="BL89" s="2" t="inlineStr"/>
+      <c r="BK89" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -17292,28 +18240,32 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -17357,7 +18309,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -17366,7 +18318,11 @@
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr"/>
-      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1683d30ce8fe40acb8ff48bcedc0fee4</t>
+        </is>
+      </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
           <t>a9b6f8add65767e20c2a3bbf</t>
@@ -17387,7 +18343,11 @@
       <c r="AL90" s="2" t="inlineStr"/>
       <c r="AM90" s="2" t="inlineStr"/>
       <c r="AN90" s="2" t="inlineStr"/>
-      <c r="AO90" s="2" t="inlineStr"/>
+      <c r="AO90" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP90" s="2" t="inlineStr"/>
       <c r="AQ90" s="2" t="inlineStr"/>
       <c r="AR90" s="2" t="inlineStr"/>
@@ -17423,10 +18383,22 @@
         </is>
       </c>
       <c r="BH90" s="2" t="inlineStr"/>
-      <c r="BI90" s="2" t="inlineStr"/>
+      <c r="BI90" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ90" s="2" t="inlineStr"/>
-      <c r="BK90" s="2" t="inlineStr"/>
-      <c r="BL90" s="2" t="inlineStr"/>
+      <c r="BK90" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -17854,28 +18826,32 @@
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -17919,7 +18895,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -17928,7 +18904,11 @@
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr"/>
-      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>9c46ad2d81734cef8d8541cf2d49e517</t>
+        </is>
+      </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
           <t>371ce04b44020b9028bccf83</t>
@@ -17949,7 +18929,11 @@
       <c r="AL93" s="2" t="inlineStr"/>
       <c r="AM93" s="2" t="inlineStr"/>
       <c r="AN93" s="2" t="inlineStr"/>
-      <c r="AO93" s="2" t="inlineStr"/>
+      <c r="AO93" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP93" s="2" t="inlineStr"/>
       <c r="AQ93" s="2" t="inlineStr"/>
       <c r="AR93" s="2" t="inlineStr"/>
@@ -17993,10 +18977,22 @@
         </is>
       </c>
       <c r="BH93" s="2" t="inlineStr"/>
-      <c r="BI93" s="2" t="inlineStr"/>
+      <c r="BI93" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ93" s="2" t="inlineStr"/>
-      <c r="BK93" s="2" t="inlineStr"/>
-      <c r="BL93" s="2" t="inlineStr"/>
+      <c r="BK93" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -18032,28 +19028,32 @@
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -18097,7 +19097,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -18106,7 +19106,11 @@
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr"/>
-      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>3deb0894d4bf4104bf36233a5680e243</t>
+        </is>
+      </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
           <t>371ce04b44020b9028bccf83</t>
@@ -18127,7 +19131,11 @@
       <c r="AL94" s="2" t="inlineStr"/>
       <c r="AM94" s="2" t="inlineStr"/>
       <c r="AN94" s="2" t="inlineStr"/>
-      <c r="AO94" s="2" t="inlineStr"/>
+      <c r="AO94" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP94" s="2" t="inlineStr"/>
       <c r="AQ94" s="2" t="inlineStr"/>
       <c r="AR94" s="2" t="inlineStr"/>
@@ -18171,10 +19179,22 @@
         </is>
       </c>
       <c r="BH94" s="2" t="inlineStr"/>
-      <c r="BI94" s="2" t="inlineStr"/>
+      <c r="BI94" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ94" s="2" t="inlineStr"/>
-      <c r="BK94" s="2" t="inlineStr"/>
-      <c r="BL94" s="2" t="inlineStr"/>
+      <c r="BK94" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -18210,28 +19230,32 @@
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -18275,7 +19299,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -18284,7 +19308,11 @@
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr"/>
-      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>9294d3c0a3fe460e8739aaa983b5f809</t>
+        </is>
+      </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
           <t>23057bd9d478c23d5f5a399c</t>
@@ -18305,7 +19333,11 @@
       <c r="AL95" s="2" t="inlineStr"/>
       <c r="AM95" s="2" t="inlineStr"/>
       <c r="AN95" s="2" t="inlineStr"/>
-      <c r="AO95" s="2" t="inlineStr"/>
+      <c r="AO95" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP95" s="2" t="inlineStr"/>
       <c r="AQ95" s="2" t="inlineStr"/>
       <c r="AR95" s="2" t="inlineStr"/>
@@ -18349,10 +19381,22 @@
         </is>
       </c>
       <c r="BH95" s="2" t="inlineStr"/>
-      <c r="BI95" s="2" t="inlineStr"/>
+      <c r="BI95" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ95" s="2" t="inlineStr"/>
-      <c r="BK95" s="2" t="inlineStr"/>
-      <c r="BL95" s="2" t="inlineStr"/>
+      <c r="BK95" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -18388,28 +19432,32 @@
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -18453,7 +19501,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -18462,7 +19510,11 @@
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr"/>
-      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>fef25e82d07b41ac854194e83ef8d451</t>
+        </is>
+      </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
           <t>297f7906e78168ac6cdb5eac</t>
@@ -18483,7 +19535,11 @@
       <c r="AL96" s="2" t="inlineStr"/>
       <c r="AM96" s="2" t="inlineStr"/>
       <c r="AN96" s="2" t="inlineStr"/>
-      <c r="AO96" s="2" t="inlineStr"/>
+      <c r="AO96" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP96" s="2" t="inlineStr"/>
       <c r="AQ96" s="2" t="inlineStr"/>
       <c r="AR96" s="2" t="inlineStr"/>
@@ -18519,10 +19575,22 @@
         </is>
       </c>
       <c r="BH96" s="2" t="inlineStr"/>
-      <c r="BI96" s="2" t="inlineStr"/>
+      <c r="BI96" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ96" s="2" t="inlineStr"/>
-      <c r="BK96" s="2" t="inlineStr"/>
-      <c r="BL96" s="2" t="inlineStr"/>
+      <c r="BK96" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -18752,28 +19820,32 @@
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -18817,7 +19889,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -18826,7 +19898,11 @@
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr"/>
-      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>bb6aeb767245471d9d3f3d12f19c2756</t>
+        </is>
+      </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
           <t>d5aa3c2bbe1791768851d76a</t>
@@ -18847,7 +19923,11 @@
       <c r="AL98" s="2" t="inlineStr"/>
       <c r="AM98" s="2" t="inlineStr"/>
       <c r="AN98" s="2" t="inlineStr"/>
-      <c r="AO98" s="2" t="inlineStr"/>
+      <c r="AO98" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP98" s="2" t="inlineStr"/>
       <c r="AQ98" s="2" t="inlineStr"/>
       <c r="AR98" s="2" t="inlineStr"/>
@@ -18883,10 +19963,22 @@
         </is>
       </c>
       <c r="BH98" s="2" t="inlineStr"/>
-      <c r="BI98" s="2" t="inlineStr"/>
+      <c r="BI98" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ98" s="2" t="inlineStr"/>
-      <c r="BK98" s="2" t="inlineStr"/>
-      <c r="BL98" s="2" t="inlineStr"/>
+      <c r="BK98" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -19139,13 +20231,17 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -19198,7 +20294,11 @@
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr"/>
-      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>9578acd89dcd4e83b945542567d0ad45</t>
+        </is>
+      </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
           <t>19a933a29d88c973aba3cd78</t>
@@ -19219,7 +20319,11 @@
       <c r="AL100" s="2" t="inlineStr"/>
       <c r="AM100" s="2" t="inlineStr"/>
       <c r="AN100" s="2" t="inlineStr"/>
-      <c r="AO100" s="2" t="inlineStr"/>
+      <c r="AO100" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP100" s="2" t="inlineStr"/>
       <c r="AQ100" s="2" t="inlineStr"/>
       <c r="AR100" s="2" t="inlineStr"/>
@@ -19265,8 +20369,16 @@
       <c r="BH100" s="2" t="inlineStr"/>
       <c r="BI100" s="2" t="inlineStr"/>
       <c r="BJ100" s="2" t="inlineStr"/>
-      <c r="BK100" s="2" t="inlineStr"/>
-      <c r="BL100" s="2" t="inlineStr"/>
+      <c r="BK100" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -20086,28 +21198,32 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -20151,7 +21267,7 @@
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -20160,7 +21276,11 @@
         </is>
       </c>
       <c r="AA105" s="2" t="inlineStr"/>
-      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>c2fb783404c24f7f833945b8b978aff1</t>
+        </is>
+      </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>b7d3578dd4a8869bec411ce5</t>
@@ -20181,7 +21301,11 @@
       <c r="AL105" s="2" t="inlineStr"/>
       <c r="AM105" s="2" t="inlineStr"/>
       <c r="AN105" s="2" t="inlineStr"/>
-      <c r="AO105" s="2" t="inlineStr"/>
+      <c r="AO105" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP105" s="2" t="inlineStr"/>
       <c r="AQ105" s="2" t="inlineStr"/>
       <c r="AR105" s="2" t="inlineStr"/>
@@ -20225,10 +21349,22 @@
         </is>
       </c>
       <c r="BH105" s="2" t="inlineStr"/>
-      <c r="BI105" s="2" t="inlineStr"/>
+      <c r="BI105" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ105" s="2" t="inlineStr"/>
-      <c r="BK105" s="2" t="inlineStr"/>
-      <c r="BL105" s="2" t="inlineStr"/>
+      <c r="BK105" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -20652,28 +21788,32 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -20717,7 +21857,7 @@
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
@@ -20726,7 +21866,11 @@
         </is>
       </c>
       <c r="AA108" s="2" t="inlineStr"/>
-      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>fe610996b456461291c9e0408c8200f2</t>
+        </is>
+      </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
           <t>b866c313bf45328c54303129</t>
@@ -20747,7 +21891,11 @@
       <c r="AL108" s="2" t="inlineStr"/>
       <c r="AM108" s="2" t="inlineStr"/>
       <c r="AN108" s="2" t="inlineStr"/>
-      <c r="AO108" s="2" t="inlineStr"/>
+      <c r="AO108" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP108" s="2" t="inlineStr"/>
       <c r="AQ108" s="2" t="inlineStr"/>
       <c r="AR108" s="2" t="inlineStr"/>
@@ -20791,10 +21939,22 @@
         </is>
       </c>
       <c r="BH108" s="2" t="inlineStr"/>
-      <c r="BI108" s="2" t="inlineStr"/>
+      <c r="BI108" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ108" s="2" t="inlineStr"/>
-      <c r="BK108" s="2" t="inlineStr"/>
-      <c r="BL108" s="2" t="inlineStr"/>
+      <c r="BK108" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
